--- a/KaptureConfigs/OtherDocs/DMTKapture_Content_Transformation_Checklist.xlsx
+++ b/KaptureConfigs/OtherDocs/DMTKapture_Content_Transformation_Checklist.xlsx
@@ -18,7 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$L$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$L$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Display by document type'!$A$1:$I$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Legacy cleaning per process'!$A$1:$I$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Open points'!$A$1:$F$15</definedName>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1364,296 +1364,302 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Dead links: href="javascript:void(0)" / "#" / ""</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>All markets, all HTML / ENT content</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>&lt;a class="ewd_mlink" href="javascript:void(0)"&gt;text&lt;span class="invisible"&gt;ewd_type=...&lt;/span&gt;&lt;/a&gt; (MC familia van e-WD links: 4,953 in 559 files); &lt;a href="#"&gt;; &lt;a href=""&gt;</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>javascript:void(0) treated as an inner link: &lt;locale&gt;\...\html\javascript:void(0) (never mapped)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>href="#" - a dead link, NOT tracked as an inner link (no INNER_LINKS_REPORT row, no lookup); text and spans kept. Anchors #name (B5), javascript:openAnotherTab (B1 / B2) and real links are unchanged.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Dead link</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>YES (user rule 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>mc/utils/ConversionUtils.isDeadLinkHref + prepareInnerLinkPaths (used by MC, MME and MNAO)</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1) INNER_LINKS_REPORT.xlsx: no ...\javascript:void(0) rows
+2) Kapture document: href="#"
+3) no Kapture 400 "Potentially malicious input"</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>MC Dev 5750: 5,012 familia van documents refused by Kapture (javascript: in the rewritten href) -&gt; fixed; 5757: 5,017 / 5,017 loaded, 0 javascript rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>window.js</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>WD HTML_MC (html folder, Flash pages)</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Quoted html / pdf addresses "/library/MAZDA/..."</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Copied as is (legacy MC window.js operation writes nothing)</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>OKAssets copy: every quoted "/library/ -&gt; "/content/library/ (byte-preserving, idempotent). Source content is not touched.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Page opens from OKAssets with this window.js - no extra handling</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>mc/utils/XcopyUtil (html movement) -&gt; WiringDiagramUtils.prefixOkAssetsContextInWindowJS</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>1) grep the OKAssets copy: no "/library/ left, "/content/library/ present
 2) job log: count of addresses changed
 3) WINDOW_JS_REPORT.xlsx</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Decision 2026-10-03.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>voltageMAP.js</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>WD HTML5 (html5/js), MC</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>':'/newm_&lt;model&gt;/.../xyz.ent'</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>dokinfoctr/mazdagms3/index?page=detail_mc&amp;id=SM1234567 (not mapped: ...&amp;id=)</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>mazdagms3/content/SM1234567 (not mapped: mazdagms3/content/)
 = GMS3_INFOCENTER_APPLICATION_CONTENT + LINK_URL_MC_WINDOW_JS + id</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>OKAssets file NEVER changed by the preview (mazdagms3 uses the same files). The preview page copy overrides window.open: mazdagms3/content/&lt;id&gt; -&gt; opens the document in the right pane, or modal 'not part of this job'</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>YES - URL pattern</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>XcopyUtil (html5 movement) -&gt; WiringDiagramUtils.performVoltageMapJSOperation; PreviewPageWriter.PAGE_SCRIPT_SOURCE</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>VOLTAGE_MAP_JS_REPORT.xlsx SUCCESS/FAILURE per link; open a voltage link in the preview</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Only .ent targets are converted.</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>voltagelinkMAP.js</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>WD HTML5 (html5/js), MC</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>As C2</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>As C2</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>As C2</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>As C2</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>YES - URL pattern</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>WiringDiagramUtils.performVoltageMapLinkJSOperation</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>VOLTAGE_LINK_MAP_JS_REPORT.xlsx; the viewer's voltage dialog in the preview</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Other html5 js files (not common.js)</t>
+          <t>voltagelinkMAP.js</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>WD HTML5 (html5/js)</t>
+          <t>WD HTML5 (html5/js), MC</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>"../conn/" or "conn/"</t>
+          <t>As C2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-&gt; /library/MAZDA/WIRING_DIAGRAMS/&lt;loc&gt;/&lt;model&gt;/&lt;mt&gt;/&lt;fl&gt;/&lt;mat&gt;/html5/conn/</t>
+          <t>As C2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Same as Prod (no /content)</t>
+          <t>As C2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Read from OKAssets as written</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>As C2</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>YES - URL pattern</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>WiringDiagramUtils.updateJSContentForHTML5</t>
+          <t>WiringDiagramUtils.performVoltageMapLinkJSOperation</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>When a model with a conn folder is processed: browser network tab - no 404 on /library/.../conn/</t>
+          <t>VOLTAGE_LINK_MAP_JS_REPORT.xlsx; the viewer's voltage dialog in the preview</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>The prod CX-5 sample js has NO conn/ references, so nothing changes today - Open points O4.</t>
-        </is>
-      </c>
+      <c r="L19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PDF attachment</t>
+          <t>Other html5 js files (not common.js)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SM / OSM PDF documents</t>
+          <t>WD HTML5 (html5/js)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>&lt;mat&gt;_PDF/pdf/abc.pdf</t>
+          <t>"../conn/" or "conn/"</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>InfoManager attachment; PDF also moved to live/staging folders</t>
+          <t>-&gt; /library/MAZDA/WIRING_DIAGRAMS/&lt;loc&gt;/&lt;model&gt;/&lt;mt&gt;/&lt;fl&gt;/&lt;mat&gt;/html5/conn/</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>ATTACHMENTS { ATTACHMENT_TITLE = raw title, ATTACHMENT = file upload }. No live/staging copy.</t>
+          <t>Same as Prod (no /content)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Copied to DMT_PREVIEW/&lt;job&gt;/files/&lt;document id&gt;/abc.pdf; right pane shows the PDF; header link 'abc.pdf' opens / downloads it</t>
+          <t>Read from OKAssets as written</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Carrier only</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>KaptureArticleBuilder.addPdfAttachments; PreviewBuilder.copyPdf</t>
+          <t>WiringDiagramUtils.updateJSContentForHTML5</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Kapture: attachment present (a 2xx on the article says nothing about attachments); preview: PDF opens</t>
+          <t>When a model with a conn folder is processed: browser network tab - no 404 on /library/.../conn/</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Kapture 500s when the file name contains '..' (shared matrix row 18).</t>
+          <t>The prod CX-5 sample js has NO conn/ references, so nothing changes today - Open points O4.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1663,27 +1669,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>WD PDF documents</t>
+          <t>SM / OSM PDF documents</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>&lt;mat&gt;/pdf/abc.pdf</t>
+          <t>&lt;mat&gt;_PDF/pdf/abc.pdf</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>InfoManager attachment</t>
+          <t>InfoManager attachment; PDF also moved to live/staging folders</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>ATTACHMENT = file upload (no ATTACHMENTS group, no title). Partial update: only TITLE + ATTACHMENT; the HTML file's attributes stay.</t>
+          <t>ATTACHMENTS { ATTACHMENT_TITLE = raw title, ATTACHMENT = file upload }. No live/staging copy.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>As D1</t>
+          <t>Copied to DMT_PREVIEW/&lt;job&gt;/files/&lt;document id&gt;/abc.pdf; right pane shows the PDF; header link 'abc.pdf' opens / downloads it</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1693,79 +1699,191 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>KaptureArticleBuilder.wdAttachment / overlayPartialWiringDiagramUpdate</t>
+          <t>KaptureArticleBuilder.addPdfAttachments; PreviewBuilder.copyPdf</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>As D1</t>
+          <t>Kapture: attachment present (a 2xx on the article says nothing about attachments); preview: PDF opens</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Kapture 500s when the file name contains '..' (shared matrix row 18).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>PDF attachment</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>WD PDF documents</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>&lt;mat&gt;/pdf/abc.pdf</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>InfoManager attachment</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>ATTACHMENT = file upload (no ATTACHMENTS group, no title). Partial update: only TITLE + ATTACHMENT; the HTML file's attributes stay.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>As D1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Carrier only</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>KaptureArticleBuilder.wdAttachment / overlayPartialWiringDiagramUpdate</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>As D1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>OKAssets copies</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>All channels</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Source folders html / html5 / image / pdf / djvu / conn / css / js / img / print ...</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Copied under /library/MAZDA/&lt;CH&gt;/&lt;loc&gt;/... (folder names lower-cased)</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Same, physical root SERVER_OKASSETS_PHYSICAL_PATH (MC Dev /s3kapture/ROOT/resources/sites/KAPTURE/content/)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Served at /content/library/...</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Root only</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>StartMCConversionImpl.startProcessingOKAssets; XcopyUtil.copyFilesToServer</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Files present at the physical path; transaction report OKAssets counts</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>OEM content: see E4.</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Metadata / attribute files (by name START + extension, case-insensitive)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>All markets - Schedule counts, conversion, OKAssets copy</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>vin*.txt, d*.txt (not delete.txt), cd*.txt, scmvin*.txt, esicat.txt; delete.txt, leftmenu.txt, vin*.ent, vin_attribute*.ent; window.js</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Schedule count skipped any file whose name CONTAINED Vin / Delete / left / window / esicat (skip.items.pattern) - the conversion did not, so Total &lt; Processed (e.g. RM100000001GVIN.html)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>vin*.txt / d*.txt / cd*.txt / scmvin*.txt / esicat.txt: metadata, never a document. delete.txt / leftmenu.txt / vin*.ent / vin_attribute*.ent: ignored everywhere (not a document, not counted, not copied to OKAssets). window.js (exact): not a document, still copied (C1). Names that only CONTAIN a word are normal: RM100000001GVIN.html, id0102q200vin.ent, window_resize.js, arrow_left.svg.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>YES (user rule 2026-10-24)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>utils/MetadataFiles (keys file.vin.ent, file.scm.vin.ent, file.name.displayorder, file.name.cdprocessing, file.name.esicat, file.name.delete, file.leftment.txt, file.name.window.js, extension.txt / .ent); servlet/Schedule.skipAttributesFile; Start*ConversionImpl vin.txt detection; mc/utils + conversion/utils XcopyUtil. skip.items.pattern removed.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>History / Item Details: DOCUMENTS Total = Processed + Failed (MC Dev 5757 familia van HTML was 5016 / 5017)</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L22"/>
+  <autoFilter ref="A1:L24"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NOT OK,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5042,7 +5160,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>vin.txt, vin1.txt ... in the facelift folder (file.vin.ent + .txt, not scmvin); a line applies when manual + FL + material match; 11 fields incl. model and year (a line with fewer fields is a VIN file issue)</t>
+          <t>vin*.txt in the facelift folder (name starts with vin, ends .txt - D4; scmvin*.txt is the MME SCM file); a line applies when manual + FL + material match; 11 fields incl. model and year (a line with fewer fields is a VIN file issue)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -5063,7 +5181,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>vin.ent / vin_attribute.ent are no longer read (user 2026-10-06).</t>
+          <t>vin.ent / vin_attribute.ent are no longer read (user 2026-10-06); since 2026-10-24 vin*.ent / vin_attribute*.ent are ignored everywhere (D4).</t>
         </is>
       </c>
     </row>
